--- a/output/pdf_financials_xlsx/ADP.xlsx
+++ b/output/pdf_financials_xlsx/ADP.xlsx
@@ -986,13 +986,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.124483</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.184594</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.009618</v>
       </c>
     </row>
     <row r="35">
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.124483</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.184594</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.009618</v>
       </c>
     </row>
     <row r="37">
@@ -1210,13 +1210,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.138983</v>
+        <v>0.0145</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.184594</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.009618</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/ADP.xlsx
+++ b/output/pdf_financials_xlsx/ADP.xlsx
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.009429999999999999</v>
+        <v>0.00958</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.07234</v>
+        <v>0.077436</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.094334</v>
+        <v>0.096149</v>
       </c>
     </row>
     <row r="8">
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.009429999999999999</v>
+        <v>0.00958</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.07234</v>
+        <v>0.077436</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.094334</v>
+        <v>0.096149</v>
       </c>
     </row>
     <row r="11">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.07234</v>
+        <v>-0.077436</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.094334</v>
+        <v>-0.096149</v>
       </c>
     </row>
     <row r="12">
@@ -3243,7 +3243,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -4148,7 +4152,11 @@
           <t>Deferred tax (recovery)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E47" s="5" t="n">
         <v>0.011</v>
       </c>
@@ -4898,7 +4906,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E71" s="5" t="n">
         <v>0.00015</v>
       </c>
